--- a/prompt.xlsx
+++ b/prompt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MohitVerma\Desktop\git\translation\SaS-to-python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{518500D9-36F0-4120-AF57-4C64C3DB44EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D822126-1FED-419B-B4AC-30E075171B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="prompt dictionary" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="56">
   <si>
     <t>Sr.No.</t>
   </si>
@@ -216,6 +216,143 @@
   </si>
   <si>
     <t>provide the guidelines clearly to avoid the hallucination</t>
+  </si>
+  <si>
+    <t>I’m going to upload an Excel file (.xlsx). 
+Please:
+1) Detect the sheets and ask me which to use (default to the first if I don’t specify).
+2) Load the data, infer data types, and summarize: row/column counts, missing values by column, basic stats for numeric columns, top categories for categorical columns.
+3) Flag potential data quality issues (duplicates, outliers, inconsistent categories, date parsing).
+4) Produce quick insights: correlations, key distributions, time trends if a date column exists.
+5) Suggest 3–5 business-oriented questions the dataset can answer next.
+Wait for me to upload the Excel file before starting, then show results step by step.</t>
+  </si>
+  <si>
+    <t>Exploratory Data Analysis (EDA)</t>
+  </si>
+  <si>
+    <t>I’ll upload an Excel workbook. 
+Please:
+1) Let me pick the sheet, then identify likely ID, date/time, numeric metric, and categorical dimensions.
+2) Ask me which 3–5 KPIs to track (or propose sensible defaults), then compute: total, average, min/max, and MoM/YoY if dates exist.
+3) Create a textual “dashboard” summary with bullet points (trends, spikes, anomalies).
+4) Generate simple charts (distribution of main metric, trend over time, top/bottom categories) and describe them.
+5) Export a clean KPI table (CSV) and a short written executive summary (TXT or Markdown).
+Wait for my Excel upload first, then proceed.</t>
+  </si>
+  <si>
+    <t>KPI Snapshot &amp; Mini “Dashboard” Summary</t>
+  </si>
+  <si>
+    <t>Modeling / Forecast or Driver Analysis</t>
+  </si>
+  <si>
+    <t>I will upload an Excel file now. 
+Please:
+1) Ask me to choose the target column (what we want to predict/forecast) and confirm the date column if forecasting.
+2) Clean data (missing values, duplicates, obvious outliers) and document what you changed.
+3) If time series: split train/test by time and fit a simple baseline forecast; if tabular: fit a baseline model (e.g., linear/boosted tree) with proper train/test split.
+4) Report performance metrics (e.g., MAE/RMSE for regression, accuracy/AUC if classification) and a quick feature/driver importance readout.
+5) Provide 2–3 actionable recommendations and save key outputs (predictions and feature importances) to downloadable CSVs.
+Hold until I upload the Excel workbook, then guide me through the choices.</t>
+  </si>
+  <si>
+    <t>I will upload an Excel workbook (.xlsx) with loan-level data.
+Please:
+1) Let me choose the sheet; detect schema (loan_id, origination_date, maturity_date, balance, rate, product, borrower_segment, region, DPD/bucket, status, defaults, recovery, vintage, etc.).
+2) Produce a concise Markdown report with:
+   - # Executive Summary (3–5 bullets)
+   - ## Portfolio Snapshot: totals, avg balance/rate/tenor; product/segment mix table
+   - ## Asset Quality: NPL ratio, PAR30/60/90, charge-off rate, cure rate; vintage default curves
+   - ## Risk Metrics: PD/LGD/EAD proxies if derivable; loss rate by segment
+   - ## Drivers &amp; Insights: top risk drivers (e.g., region, product, LTV proxy), notable cohorts
+   - ## Actions: 3–5 targeted recommendations
+3) Include compact Markdown tables for KPIs and cohort/vintage summaries.
+4) Keep the narrative tight (≤250 words total). 
+Wait for my Excel upload before starting; then ask me for the sheet and any column mappings you need.</t>
+  </si>
+  <si>
+    <t>Credit Risk &amp; Loan Portfolio Performance</t>
+  </si>
+  <si>
+    <t>Payments Fraud Monitoring &amp; Alerts Quality</t>
+  </si>
+  <si>
+    <t>I will upload an Excel workbook (.xlsx) with transactions and labels/scores.
+Please:
+1) Let me choose the sheet; infer columns (txn_id, timestamp, amount, channel, merchant, card/bin, customer_id, geo, model_score, is_fraud, case_outcome).
+2) Produce a concise Markdown report with:
+   - # Executive Summary (3–5 bullets)
+   - ## Fraud KPIs: attempted vs confirmed fraud, fraud rate, dollar loss, attack concentration (merchant/channel)
+   - ## Detection Quality: precision/recall, ROC-AUC, alert volume, false-positive rate, case SLA
+   - ## Patterns: time-of-day/day-of-week spikes, high-risk segments, top merchants/channels
+   - ## Actions: rules/model tuning suggestions (score threshold, features), ops workflow tweaks
+3) Provide 2 compact Markdown tables: KPI summary and Top-10 risky entities.
+4) ≤200 words narrative; use simple percentages with two decimals.
+Wait for my Excel upload; then request the sheet and confirm label/score columns.</t>
+  </si>
+  <si>
+    <t>I will upload an Excel workbook (.xlsx) with deposit and balance-sheet data.
+Please:
+1) Let me pick the sheet; map columns (account_id, product, balance, rate_paid, customer_segment, open_date, churn_flag, daily_balances, FTP_rate, securities, loans, HQLA, outflows).
+2) Create a concise Markdown report with:
+   - # Executive Summary (3–5 bullets)
+   - ## Deposits: growth, inflows/outflows, weighted avg rate, beta vs benchmark (if dates exist)
+   - ## Margin Snapshot: NIM proxy (interest income – interest expense)/avg earning assets, deposit mix shift
+   - ## Liquidity: LCR/NSFR approximations if derivable; HQLA coverage; stress outflow notes
+   - ## Actions: pricing, mix, and liquidity buffer recommendations
+3) Include 2 small Markdown tables: Deposit KPIs by product; Liquidity metrics.
+4) Cap prose at ~220 words; keep formulas transparent in footnotes.
+Begin after I upload the Excel file; then ask for sheet selection and any required mappings.</t>
+  </si>
+  <si>
+    <t>Deposits, Margin &amp; ALM Liquidity</t>
+  </si>
+  <si>
+    <t>I will upload an Excel workbook (.xlsx) with customer and survey/interaction data.
+Please:
+1) Let me choose the sheet; detect columns (customer_id, tenure, products_held, balances, fees, complaints, interactions, NPS, CSAT, churn_flag, region).
+2) Produce a concise Markdown report with:
+   - # Executive Summary (3–5 bullets)
+   - ## Customer KPIs: NPS distribution, CSAT, churn rate, cross-sell penetration, fee sensitivity
+   - ## Drivers: correlation/feature-importance style read on what links to churn/NPS (e.g., fees, service wait, outages)
+   - ## Segments: top at-risk cohorts (tenure bands, region, product mix)
+   - ## Actions: 3–5 retention &amp; CX improvements with expected impact ranges
+3) Provide 2 compact Markdown tables: KPI summary; At-risk segment table (size, churn%, lift).
+4) Keep the write-up ≤225 words; plain language, no jargon.
+Start once I upload the Excel; then confirm the churn/NPS column names.</t>
+  </si>
+  <si>
+    <t>Retail Banking CX, NPS &amp; Churn Signals</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Competitor research</t>
+  </si>
+  <si>
+    <t>Analytics</t>
+  </si>
+  <si>
+    <t>Report writing</t>
+  </si>
+  <si>
+    <t>Branch &amp; ATM Network Performance / Cost-to-Serve</t>
+  </si>
+  <si>
+    <t>I will upload an Excel workbook (.xlsx) with branch/ATM performance data.
+Please:
+1) Let me pick the sheet; infer columns (branch_id, location, footfall, transactions, sales, deposits, costs, staff_count, hours, NIM contribution, complaints, ATM_uptime).
+2) Deliver a concise Markdown report with:
+   - # Executive Summary (3–5 bullets)
+   - ## Efficiency: cost-to-income, sales per FTE, transactions per hour, queue/wait proxies
+   - ## Profitability: contribution by branch decile; identify underperformers/outliers
+   - ## Service &amp; Uptime: ATM uptime %, complaint rate, SLA breaches
+   - ## Actions: optimize staffing/hours, migrate to digital, close/merge candidates, ATM maintenance priorities
+3) Include 2 short Markdown tables: Branch deciles (KPIs); Bottom-10 branches with suggested actions.
+4) Narrative ≤200 words; emphasize decisions and next steps.
+Proceed after I upload the Excel file; then ask me for the sheet and any required mappings.</t>
   </si>
 </sst>
 </file>
@@ -278,7 +415,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -290,6 +427,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -570,16 +709,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:F8"/>
+  <dimension ref="B2:G16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="43" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.08984375" customWidth="1"/>
+    <col min="5" max="5" width="22.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="43" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -587,16 +727,19 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B3" s="2">
         <v>1</v>
       </c>
@@ -604,31 +747,37 @@
         <v>5</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B4" s="2">
         <v>2</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B5" s="2">
         <v>3</v>
       </c>
@@ -636,16 +785,19 @@
         <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B6" s="2">
         <v>4</v>
       </c>
@@ -653,16 +805,19 @@
         <v>14</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B7" s="2">
         <v>5</v>
       </c>
@@ -670,16 +825,19 @@
         <v>18</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="2">
         <v>6</v>
       </c>
@@ -687,13 +845,144 @@
         <v>22</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B9" s="5">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B10" s="5">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B11" s="2">
+        <v>9</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B12" s="2">
+        <v>10</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B13" s="2">
+        <v>11</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B14" s="2">
+        <v>12</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B15" s="2">
+        <v>13</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B16" s="5">
+        <v>14</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/prompt.xlsx
+++ b/prompt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MohitVerma\Desktop\git\translation\SaS-to-python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D822126-1FED-419B-B4AC-30E075171B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{253AFE60-41A5-44EC-B1DF-F7DDD0A4293D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="57">
   <si>
     <t>Sr.No.</t>
   </si>
@@ -353,6 +353,9 @@
 3) Include 2 short Markdown tables: Branch deciles (KPIs); Bottom-10 branches with suggested actions.
 4) Narrative ≤200 words; emphasize decisions and next steps.
 Proceed after I upload the Excel file; then ask me for the sheet and any required mappings.</t>
+  </si>
+  <si>
+    <t>demo</t>
   </si>
 </sst>
 </file>
@@ -388,7 +391,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -411,11 +414,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -427,8 +441,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -709,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G16"/>
+  <dimension ref="B2:G17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="14.08984375" bestFit="1" customWidth="1"/>
@@ -858,7 +871,7 @@
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B9" s="5">
+      <c r="B9" s="2">
         <v>7</v>
       </c>
       <c r="C9" s="2"/>
@@ -868,13 +881,13 @@
       <c r="E9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6" t="s">
+      <c r="F9" s="2"/>
+      <c r="G9" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B10" s="5">
+      <c r="B10" s="2">
         <v>8</v>
       </c>
       <c r="C10" s="2"/>
@@ -884,8 +897,8 @@
       <c r="E10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6" t="s">
+      <c r="F10" s="2"/>
+      <c r="G10" s="2" t="s">
         <v>38</v>
       </c>
     </row>
@@ -900,8 +913,8 @@
       <c r="E11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6" t="s">
+      <c r="F11" s="2"/>
+      <c r="G11" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -910,14 +923,14 @@
         <v>10</v>
       </c>
       <c r="C12" s="2"/>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>43</v>
       </c>
       <c r="F12" s="2"/>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="2" t="s">
         <v>42</v>
       </c>
     </row>
@@ -926,14 +939,14 @@
         <v>11</v>
       </c>
       <c r="C13" s="2"/>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F13" s="2"/>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="2" t="s">
         <v>45</v>
       </c>
     </row>
@@ -942,14 +955,14 @@
         <v>12</v>
       </c>
       <c r="C14" s="2"/>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>47</v>
       </c>
       <c r="F14" s="2"/>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="2" t="s">
         <v>46</v>
       </c>
     </row>
@@ -958,31 +971,42 @@
         <v>13</v>
       </c>
       <c r="C15" s="2"/>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>49</v>
       </c>
       <c r="F15" s="2"/>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="2" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B16" s="5">
+      <c r="B16" s="2">
         <v>14</v>
       </c>
       <c r="C16" s="2"/>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F16" s="2"/>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="2" t="s">
         <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D17" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/prompt.xlsx
+++ b/prompt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MohitVerma\Desktop\git\translation\SaS-to-python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{253AFE60-41A5-44EC-B1DF-F7DDD0A4293D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBCBE2E9-6EF8-4497-9767-2A624541087B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -391,7 +391,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -414,22 +414,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -441,7 +430,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -998,14 +986,19 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="4:7" x14ac:dyDescent="0.35">
-      <c r="D17" s="5" t="s">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B17" s="2">
+        <v>15</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="F17" s="2"/>
+      <c r="G17" s="2" t="s">
         <v>56</v>
       </c>
     </row>
